--- a/policy.xlsx
+++ b/policy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maadh\OneDrive\Desktop\serveup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0D4CDF-248A-4B1D-8615-EB7C106E6E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{4A0D4CDF-248A-4B1D-8615-EB7C106E6E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37FAAF30-D6A2-4E0D-B1B5-07478EF7BC09}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January 2022" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="April 2023" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'March 2023'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'April 2023'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'March 2023'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="1300">
   <si>
     <t>Date</t>
   </si>
@@ -3710,6 +3711,234 @@
   </si>
   <si>
     <t>Green hydrogen holds great promise for India</t>
+  </si>
+  <si>
+    <t>Education in retreat</t>
+  </si>
+  <si>
+    <t>From 'Finlandisation' to 'Natoisation'</t>
+  </si>
+  <si>
+    <t>The institutional crisis that Pakistan faces</t>
+  </si>
+  <si>
+    <t>Varying shades of 'green'</t>
+  </si>
+  <si>
+    <t>Hydro policy in a flux</t>
+  </si>
+  <si>
+    <t>E-pharmacy regulation needs nuanced policies</t>
+  </si>
+  <si>
+    <t>An improper forum</t>
+  </si>
+  <si>
+    <t>Ministry of Truth</t>
+  </si>
+  <si>
+    <t>A broken house</t>
+  </si>
+  <si>
+    <t>Why Sri Lanka's proposed anti-terror law faces widespread criticism</t>
+  </si>
+  <si>
+    <t>The long road to women empowerment</t>
+  </si>
+  <si>
+    <t>The digital space gives wings to women entrepreneurs</t>
+  </si>
+  <si>
+    <t>Inflation versus growth: RBI's dilemma</t>
+  </si>
+  <si>
+    <t>What they don't tell you about India's poverty numbers</t>
+  </si>
+  <si>
+    <t>Cash combustion rates could separate startups</t>
+  </si>
+  <si>
+    <t>How private capital can be made to work for global public goods</t>
+  </si>
+  <si>
+    <t>MSMEs selling online need simpler GST rules</t>
+  </si>
+  <si>
+    <t>The knotty business of running cooperatives</t>
+  </si>
+  <si>
+    <t>Lessons for India from US bank debacle</t>
+  </si>
+  <si>
+    <t>Bias in higher education</t>
+  </si>
+  <si>
+    <t>ChatGPT, a double-edged weapon</t>
+  </si>
+  <si>
+    <t>Reducing inflation without raising interest rates</t>
+  </si>
+  <si>
+    <t>A potent channel</t>
+  </si>
+  <si>
+    <t>Academic freedom and the crisis in higher education</t>
+  </si>
+  <si>
+    <t>An enforced silence cannot solve India's problems</t>
+  </si>
+  <si>
+    <t>Finland's journey, from neutral to NATO</t>
+  </si>
+  <si>
+    <t>Do the wealthy influence policy-making more across all forms of democracy?</t>
+  </si>
+  <si>
+    <t>Free speech: Not Supreme Court, but the people</t>
+  </si>
+  <si>
+    <t>Too Yuan to Rock'n'Roll</t>
+  </si>
+  <si>
+    <t>Milk will spill:  Amul vs. Nandini in Namma Bengaluru</t>
+  </si>
+  <si>
+    <t>Learn from traditional farming</t>
+  </si>
+  <si>
+    <t>Setting the G20 agenda</t>
+  </si>
+  <si>
+    <t>Why we learn wrong lessons from China</t>
+  </si>
+  <si>
+    <t>The Populist Raj</t>
+  </si>
+  <si>
+    <t>Don't bet with ChatGPT</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>policy</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>brief</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iFkMbMj1YPsBsb6afqShDORkKH9thkKW/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rW1n1xQ2FtF4x6YzT07PN1RE2fbBZev3/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uxTwBOe1jcI_HOUWzZhc62uMDmD5asDR/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VbWu8whAi1zZoxEBehm-j6M0G3cbVabz/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JMHdU3xgRiZH7xyI_ov6wbII53EXkFWD/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1v2vBDQZu-_idW29de-I0KWbPNXqoPrhr/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fZz0CgqGbPown9PFpvJm3uwoq313w5Xx/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1W1Yg_mnIN3O3KiEo66N2PusgbJ8D0UNa/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JLP-8pTyRcJijxsfjgX8lte0fmgQSS8q/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ruM4yDai77pVnDXU8cyFzhOBsvbiGT8l/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/115VEO4JzZLzmGNo4NOO_H-bDq73eBCBh/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rh62icFC2bMIS5EOiKZmRFvPRuilItDJ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1H5YP8X96S-m3Nk17PH13pLyO79AGLfJ-/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MDDM8vtefoT3EeFo0zdbdgzlYvhy9ZfN/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uNpM9ubuCnwdp3d8mRdYw7jg7rK2xlSm/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kX4b8IWdBAmLnyDVjPD5iKKYKavouDmp/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FLcq_1rLunA52nxcuzalX4TOjF6eozqk/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QORlQuCDtauCcP5lXdeZZ7QtgX91QS9b/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12P737JhmqaZU9c5c0cqOIk378ZrROVDR/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1F0ETgHbuWoAnI0BdwSh9BduzFZ53vcut/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jjy_90lFdYJE9Ct5Nc_UA61vrXCRYdRh/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19ZAQCn_wdy3GXOR65uLlSJpumWjYYR6B/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nAJDuYLaVmZBpL0_m38wEc4krPBH2o5P/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rTYvody8v_SiIDjUxWrEn7PkYYVaLpAo/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rfRCmK7xD4jcVV8CcfpAP8DIstrFE0AT/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KwlNd576bwjhhi97fgmcT8rObnOWUeEs/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Aw8mvPeGlL4ckk65SXM-lzMqvcTSybER/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12WDuNzNiFqb13jvneWvMDawuVBmO9Rku/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1olyRnRyuLHbtJ93_9R9Kc4NPl7FmBFGF/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A59YWF7Cd_OX-p2VtKjosdkXWYMJ3uPa/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LMkKei06k9_pjGzLE1y6_hNdK-i_Ig6t/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DOICv7GEFSoo27ET2TJQPKDNURFmY8xJ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vrUlgqs1bh4ndVUUHB8-PmTKiGA2-ofJ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DkcVjE3SXqLuCvIb7TCaJgY-0LWUKIzS/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jfvBEUckIceGdXETKIc-W8G-xMQxyWjt/view?usp=share_link</t>
   </si>
 </sst>
 </file>
@@ -3806,6 +4035,10 @@
 </file>
 
 <file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person2.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -8844,7 +9077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031D3F6-D661-4A89-A608-6121CB87C06C}">
-  <dimension ref="A1:F329"/>
+  <dimension ref="A1:G329"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -8854,25 +9087,28 @@
     <col min="5" max="5" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>1259</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="4" t="s">
-        <v>1</v>
+        <v>1260</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2</v>
+        <v>1264</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>1262</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1263</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>44995</v>
       </c>
@@ -8883,7 +9119,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>44995</v>
       </c>
@@ -8894,7 +9130,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>44995</v>
       </c>
@@ -8905,7 +9141,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>44995</v>
       </c>
@@ -8916,7 +9152,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>44995</v>
       </c>
@@ -8927,7 +9163,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>44995</v>
       </c>
@@ -8938,7 +9174,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44995</v>
       </c>
@@ -8949,7 +9185,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44995</v>
       </c>
@@ -8960,7 +9196,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44995</v>
       </c>
@@ -8971,7 +9207,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44995</v>
       </c>
@@ -8982,7 +9218,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44995</v>
       </c>
@@ -8993,7 +9229,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44995</v>
       </c>
@@ -9004,7 +9240,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44995</v>
       </c>
@@ -9015,7 +9251,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44995</v>
       </c>
@@ -9026,7 +9262,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44995</v>
       </c>
@@ -12481,46 +12717,46 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{2031D3F6-D661-4A89-A608-6121CB87C06C}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F220">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:I1" xr:uid="{2031D3F6-D661-4A89-A608-6121CB87C06C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F282"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
     <col min="2" max="2" width="3.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="53.109375" customWidth="1"/>
-    <col min="4" max="4" width="61.21875" customWidth="1"/>
+    <col min="3" max="4" width="53.109375" customWidth="1"/>
     <col min="5" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="61.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>1259</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="4" t="s">
-        <v>1</v>
+        <v>1260</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2</v>
+        <v>1264</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>1262</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1263</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45017</v>
       </c>
@@ -12531,7 +12767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45017</v>
       </c>
@@ -12542,7 +12778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45017</v>
       </c>
@@ -12553,7 +12789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45017</v>
       </c>
@@ -12564,7 +12800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45017</v>
       </c>
@@ -12575,7 +12811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45017</v>
       </c>
@@ -12586,7 +12822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45017</v>
       </c>
@@ -12597,7 +12833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45017</v>
       </c>
@@ -12608,7 +12844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45017</v>
       </c>
@@ -12619,7 +12855,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45017</v>
       </c>
@@ -12630,7 +12866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45017</v>
       </c>
@@ -12641,7 +12877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45017</v>
       </c>
@@ -12652,7 +12888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45017</v>
       </c>
@@ -12663,7 +12899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45017</v>
       </c>
@@ -12674,7 +12910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45017</v>
       </c>
@@ -12688,7 +12924,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45017</v>
       </c>
@@ -12699,7 +12935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45017</v>
       </c>
@@ -12710,7 +12946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45017</v>
       </c>
@@ -12721,7 +12957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45017</v>
       </c>
@@ -12732,7 +12968,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45017</v>
       </c>
@@ -12743,7 +12979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45017</v>
       </c>
@@ -12754,7 +12990,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45017</v>
       </c>
@@ -12765,7 +13001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45017</v>
       </c>
@@ -12776,7 +13012,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45017</v>
       </c>
@@ -12786,8 +13022,9 @@
       <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45017</v>
       </c>
@@ -12798,7 +13035,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45017</v>
       </c>
@@ -12809,7 +13046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45017</v>
       </c>
@@ -12820,7 +13057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45017</v>
       </c>
@@ -12830,8 +13067,9 @@
       <c r="C29" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45018</v>
       </c>
@@ -12842,7 +13080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45018</v>
       </c>
@@ -12853,7 +13091,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45018</v>
       </c>
@@ -15504,7 +15742,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>45025</v>
       </c>
@@ -15515,7 +15753,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>45025</v>
       </c>
@@ -15526,7 +15764,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>45025</v>
       </c>
@@ -15537,7 +15775,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>45025</v>
       </c>
@@ -15548,7 +15786,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>45025</v>
       </c>
@@ -15559,7 +15797,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>45025</v>
       </c>
@@ -15570,7 +15808,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>45025</v>
       </c>
@@ -15581,7 +15819,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>45025</v>
       </c>
@@ -15592,7 +15830,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>45025</v>
       </c>
@@ -15603,7 +15841,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>45025</v>
       </c>
@@ -15614,7 +15852,498 @@
         <v>895</v>
       </c>
     </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B283" s="2">
+        <v>1</v>
+      </c>
+      <c r="C283" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B284" s="2">
+        <v>2</v>
+      </c>
+      <c r="C284" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G284" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B285" s="2">
+        <v>3</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B286" s="2">
+        <v>4</v>
+      </c>
+      <c r="C286" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G286" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B287" s="2">
+        <v>5</v>
+      </c>
+      <c r="C287" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G287" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B288" s="2">
+        <v>6</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B289" s="2">
+        <v>7</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B290" s="2">
+        <v>8</v>
+      </c>
+      <c r="C290" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G290" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B291" s="2">
+        <v>9</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B292" s="2">
+        <v>10</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G292" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B293" s="2">
+        <v>11</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B294" s="2">
+        <v>12</v>
+      </c>
+      <c r="C294" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G294" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B295" s="2">
+        <v>13</v>
+      </c>
+      <c r="C295" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G295" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B296" s="2">
+        <v>14</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G296" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B297" s="2">
+        <v>15</v>
+      </c>
+      <c r="C297" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G297" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B298" s="2">
+        <v>16</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G298" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B299" s="2">
+        <v>17</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G299" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B300" s="2">
+        <v>18</v>
+      </c>
+      <c r="C300" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G300" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B301" s="2">
+        <v>19</v>
+      </c>
+      <c r="C301" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G301" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B302" s="2">
+        <v>20</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G302" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B303" s="2">
+        <v>21</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B304" s="2">
+        <v>22</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G304" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B305" s="2">
+        <v>23</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G305" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B306" s="2">
+        <v>24</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G306" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B307" s="2">
+        <v>25</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G307" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A308" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B308" s="2">
+        <v>26</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G308" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A309" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B309" s="2">
+        <v>27</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G309" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B310" s="2">
+        <v>28</v>
+      </c>
+      <c r="C310" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G310" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A311" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B311" s="2">
+        <v>29</v>
+      </c>
+      <c r="C311" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G311" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B312" s="2">
+        <v>30</v>
+      </c>
+      <c r="C312" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G312" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A313" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B313" s="2">
+        <v>31</v>
+      </c>
+      <c r="C313" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G313" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B314" s="2">
+        <v>32</v>
+      </c>
+      <c r="C314" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G314" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A315" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B315" s="2">
+        <v>33</v>
+      </c>
+      <c r="C315" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G315" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B316" s="2">
+        <v>34</v>
+      </c>
+      <c r="C316" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G316" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A317" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B317" s="2">
+        <v>35</v>
+      </c>
+      <c r="C317" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G317" t="s">
+        <v>1265</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{4A0D4CDF-248A-4B1D-8615-EB7C106E6E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37FAAF30-D6A2-4E0D-B1B5-07478EF7BC09}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{4A0D4CDF-248A-4B1D-8615-EB7C106E6E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0E12EA7-0A62-432E-AF5F-1C310CEF9D7A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="1466">
   <si>
     <t>Date</t>
   </si>
@@ -3939,6 +3939,504 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1jfvBEUckIceGdXETKIc-W8G-xMQxyWjt/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>The Adani lesson</t>
+  </si>
+  <si>
+    <t>Reinvent tiger conservation</t>
+  </si>
+  <si>
+    <t>Britain need not apologise to India</t>
+  </si>
+  <si>
+    <t>Remembering a revolutionary</t>
+  </si>
+  <si>
+    <t>Bhutan's imperatives and India's dilemmas</t>
+  </si>
+  <si>
+    <t>On Washington's 18th St, a bank waits for change</t>
+  </si>
+  <si>
+    <t>Missing in India's AI growth plan is private investment</t>
+  </si>
+  <si>
+    <t>Charting India' s rise to $1 trillion in exports</t>
+  </si>
+  <si>
+    <t>Is SHE enterprise an oxymoron?</t>
+  </si>
+  <si>
+    <t>Ensuring scrutiny by Parliament</t>
+  </si>
+  <si>
+    <t>The arcane ways of the MPC</t>
+  </si>
+  <si>
+    <t>Signing FTAs with an eye on FDI</t>
+  </si>
+  <si>
+    <t>Build disaster-proof cities</t>
+  </si>
+  <si>
+    <t>Green Hydrogen: Clean fuel alternative for New India</t>
+  </si>
+  <si>
+    <t>Indian TV, 'hashtag' audience fragmentation</t>
+  </si>
+  <si>
+    <t>Saudi Arabia's quest for strategic autonomy</t>
+  </si>
+  <si>
+    <t>Why Dalit writing is a social movement with the power to change lives</t>
+  </si>
+  <si>
+    <t>India needs a principles-based approach to regulate AI</t>
+  </si>
+  <si>
+    <t>The Pentagon leak can make a fine case study</t>
+  </si>
+  <si>
+    <t>The G20 must help create a global financial safety net</t>
+  </si>
+  <si>
+    <t>Conundrum of working women in India: Our menfolk must step up</t>
+  </si>
+  <si>
+    <t>Europe's security landscape changing</t>
+  </si>
+  <si>
+    <t>New currency for BRICS: How feasible will it be?</t>
+  </si>
+  <si>
+    <t>Growing Taiwan-US relations rile Beijing</t>
+  </si>
+  <si>
+    <t>Ride Globalisation, Again</t>
+  </si>
+  <si>
+    <t>Lens on inflation-targeting</t>
+  </si>
+  <si>
+    <t>Why TN's online gamling Bill could clash with Centre's rules</t>
+  </si>
+  <si>
+    <t>Classroom for the future</t>
+  </si>
+  <si>
+    <t>The caste glue</t>
+  </si>
+  <si>
+    <t>The path to excellence</t>
+  </si>
+  <si>
+    <t>Regulating the regulators</t>
+  </si>
+  <si>
+    <t>The peace that could have been</t>
+  </si>
+  <si>
+    <t>Gandhian who became India's Prime Minister</t>
+  </si>
+  <si>
+    <t>Ratcheting imbroglio</t>
+  </si>
+  <si>
+    <t>Democratising the Commonwealth</t>
+  </si>
+  <si>
+    <t>Advantages of genome sequencing in healthcare</t>
+  </si>
+  <si>
+    <t>Rules of the blue economy</t>
+  </si>
+  <si>
+    <t>Prepare India for endemic Covid: Surge no big worry</t>
+  </si>
+  <si>
+    <t>New law, focus on tech can help CBI counter corruption, politics</t>
+  </si>
+  <si>
+    <t>The real bite of SC's MediaOne ruling</t>
+  </si>
+  <si>
+    <t>Rights of the Opposition</t>
+  </si>
+  <si>
+    <t>Old approach, new pact</t>
+  </si>
+  <si>
+    <t>The tri-junction problem</t>
+  </si>
+  <si>
+    <t>The poverty mystery</t>
+  </si>
+  <si>
+    <t>Building the blue economy</t>
+  </si>
+  <si>
+    <t>Changes the NCF 2023 draft proposes in the school education system</t>
+  </si>
+  <si>
+    <t>What LIGO-India will do</t>
+  </si>
+  <si>
+    <t>We must end the life-altering power of a college degree</t>
+  </si>
+  <si>
+    <t>Let's insist on full disclosure and consent for AI and algorithm use</t>
+  </si>
+  <si>
+    <t>Intermediary oversight should never be opaque</t>
+  </si>
+  <si>
+    <t>Pradhan Mantri Mudra Yojana: Credit saturation for livelihoods</t>
+  </si>
+  <si>
+    <t>How safe are the medicines we use?</t>
+  </si>
+  <si>
+    <t>Save Mission Millet before it crashes</t>
+  </si>
+  <si>
+    <t>Directing AI for better and smarter legislation</t>
+  </si>
+  <si>
+    <t>Awaiting lift-off into the Second Space Age</t>
+  </si>
+  <si>
+    <t>Existing vaccines versus new COVID variants</t>
+  </si>
+  <si>
+    <t>The population bomb that never was</t>
+  </si>
+  <si>
+    <t>Stitching it the Bangladesh way</t>
+  </si>
+  <si>
+    <t>Tune in to millet sur mera tumhara</t>
+  </si>
+  <si>
+    <t>RBI's clever turn of phrase</t>
+  </si>
+  <si>
+    <t>49 words that will change India's internet</t>
+  </si>
+  <si>
+    <t>Hydrogen mission may undermine climate goals</t>
+  </si>
+  <si>
+    <t>Intelligence for solution finding</t>
+  </si>
+  <si>
+    <t>Students are taking the climate fight to court</t>
+  </si>
+  <si>
+    <t>Wrong way to fight the battle for clean politics</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dMh54i3sRgpJD7lWLO_hJw9nlLYllbDQ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/112yVshIrHbObAG7rK2acouAcrfXQOJo4/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KW2XbfdU37TycvWrWvARP3xTuEBaUOdz/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Gr55CIDPuN231nM_JlJpoJz9Et8TurpT/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xZWpzlywM8_oX90dJfivdpqVJOTCfbxL/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wztVZoj74zNBx-82vFYtXXY6-rMnSrKH/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xxRM3_CHaT48Gqm9LyPrCCDLkLdPfhKl/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17hnsrlJ0eHhpj4DLEvaM9tnSN2fyCXZa/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QLtZoYbETe3PG7_k5ApMbS_BC3TXnSQw/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hdfL-9iYP4XBNWSbRDBFdwn0f1lADFZa/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16B9GqMVjbpNdqk90ei7nsdeFPSpsN6Je/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FkG0g2saQlW_eAQTHg8MhG_phExWVNqF/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10DwKY98eNvGIvUd7OR0MWSWwNhMdORUu/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14c4ggr-naMFHn6N_-umf5X7JCS9xQMqG/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hpS4qNmBzCXxQdoVMyoFUTK0VTEEVuyp/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1khxteZKhidEPdvFy0qQtTOvQtBUCgWQ2/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Gu88YmX6xxm1fTOgFIHEFm6hz6plPLdQ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rg7tRzyoZgs_kIMpNbOGOyUp8etjxXKw/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TKLkGUUSzU9tOtxJIYwYe9Frqf6hLIAh/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1caTxk19y4ed6KoQDh_Ea3yfy4JJ8zeGP/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OldFGWN75xosVfMmBixfOrN4KHRcB8OI/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dE6mdzs0OD-tdHEnjVI8vtTUJD73oEGC/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D-PAAc9g53-q2Q9hSyokemyZeDRqwd7D/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1B4XegRQ3YhTF815bL048IFIqMNDC2B6q/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19h7qq60hUOBlCCaUxix7OhRYukCu_GtI/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17ks0cWe2TUh0PsOo7DXoPgzIsbF5vvGu/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gzrGToLK9oI6OgUwHFMdO00x3qKoXYpj/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DagofzPJmZdws3jw0etyRzJ1EmjnFzUH/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16eN94bz3vJZMIYVwRr0qITE-EDY6eH9H/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1flPL-hvtAbwGiR_Ksgp5Rr-ukg0W-qXQ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GbgnknsdPy3nKcwhcEHnQDvn7BxtwdWR/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1twAKgNShUeK9RcxbcyMMJRpASLxNk1wX/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/102lG746U6xNaGH2w_cIPvNF5m0BNpBks/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>The community radio needs Govt support</t>
+  </si>
+  <si>
+    <t>SEBI pulls the plug on financial influencers</t>
+  </si>
+  <si>
+    <t>Ambedkar's idea of cultural nationalism</t>
+  </si>
+  <si>
+    <t>Should officers prioritise Centre over the cadre of their own states?</t>
+  </si>
+  <si>
+    <t>As India gets hotter, it's time to act 'hyper-local'</t>
+  </si>
+  <si>
+    <t>A new Asian order is emerging</t>
+  </si>
+  <si>
+    <t>An Aadhaar for land</t>
+  </si>
+  <si>
+    <t>New trade body to step up exports welcome</t>
+  </si>
+  <si>
+    <t>NAM Redux?</t>
+  </si>
+  <si>
+    <t>To calm a still-choppy SaMUDRA</t>
+  </si>
+  <si>
+    <t>That statistical rare figure, C R Rao</t>
+  </si>
+  <si>
+    <t>India under trick or threat?</t>
+  </si>
+  <si>
+    <t>Fixing legal loopholes</t>
+  </si>
+  <si>
+    <t>A giant leap</t>
+  </si>
+  <si>
+    <t>Will Germany Inc, bearish on China, turn bullish on India?</t>
+  </si>
+  <si>
+    <t>India must board the Online Dispute Resolution bus</t>
+  </si>
+  <si>
+    <t>Corporate power and Indian inflation</t>
+  </si>
+  <si>
+    <t>The role of Parliamentary Committees</t>
+  </si>
+  <si>
+    <t>A beginner's guide to the Large Hadron Collider, its functions and its future</t>
+  </si>
+  <si>
+    <t>The focus of G20 is sustainable tourism</t>
+  </si>
+  <si>
+    <t>The key to achieving sustainable growth</t>
+  </si>
+  <si>
+    <t>A Roald Dahl for every child</t>
+  </si>
+  <si>
+    <t>A tale of two cases</t>
+  </si>
+  <si>
+    <t>Aadhaar for land</t>
+  </si>
+  <si>
+    <t>Let us fund civil society organizations for the long haul</t>
+  </si>
+  <si>
+    <t>Expanding geographical spread of microfinance</t>
+  </si>
+  <si>
+    <t>R&amp;D policy at an inflexion point</t>
+  </si>
+  <si>
+    <t>More funds for adaptation of farming to climate change</t>
+  </si>
+  <si>
+    <t>Diagnosing the NPA cancer early</t>
+  </si>
+  <si>
+    <t>Quotas and the private sector</t>
+  </si>
+  <si>
+    <t>Quest for value chains and exports</t>
+  </si>
+  <si>
+    <t>We need proactive regulation to fend off SVB-like bank failures</t>
+  </si>
+  <si>
+    <t>eSanjeevani, the common man's life-saviour</t>
+  </si>
+  <si>
+    <t>Selective Deletion of history a disaster for democracy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iHwpHZOjxtqH7n1FYyO68Sxskq2RJSZL/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UzYy1kRZW6_AEhCjdGbnAV93P22CPmy2/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18r0xxsPZxP2Y9yKT_lx1e_SpMUbwrqQM/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JJk1eboGma4U7f2xpgtg6eYdFh7eBK2W/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GUuVSbFwh1uKFjOztwqoqOjFWg5CWMbj/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1e-QCL0z0aBmohYpLnK5Hi06ns3Axu8iu/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1B8bcLLTdIFfzE0uktMVhCrzw48qvL163/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lwdkIvGUUpip7U0I5enpGH3CWqft3T1Z/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/177lci5MZQ7NyW9qNJsYB2153uT23ufeD/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1o0bfeVsQO2Hfzbp64qUFYJEqCkbJc3iZ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zHmOWHLvt3LYMDcBByUbLxB13_p26Rqe/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YLKINO-7NR4kWFzD2Rh3bOfmVk1MEZta/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HWTTrdkddDgXblw_mqfzjFXxnloaO6vq/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FBdCP8CfZDJ-uvjatOZ-5mOB_7-_ecxg/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WNcMW1n8Gr6zFCfnFrhI40m3y4wGbYKQ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lWFgKEDzNPeTINotS_Sjyj_9ro-1J-Oj/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1S80igE83pNZu7rtskr_fW5urcfQeEpSz/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Hmcz7O8n7yFTUjGTwAWSTN1VJEx34qLE/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12iPS0akIu-P3nOyzbLYbMZHf0XMvcEWG/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QvuFyArvOiKqYzi0a3DCr-6LrRr97upZ/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1s3Wn8v1m1bsg9P_1vaHG5zaRYBggT8o5/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18P0jCv_ljA3JlNJU2AEWjUhKz9bgFmAg/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PsmLILKADI0LCfpaaslOe7kunVlPQ0J8/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eca-fBFabtp4s4EE0H-ZHOUMmLLJKv2y/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IrJGhet3lmQhnHKHZ8UOG7v3ECBa4OBb/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dF-afPB1dYpbs84jHppjkLl2cqBj0cDt/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/160UQMxTCvCmSDlrAMZLoLMazQZWVBL2m/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10-eAfU1pqiQPK10VHpqBGVu0zgGiW5d6/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Pq7cFk0oCVO-5aCITxVeegReee0uqCjf/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vjr0ThKxF46_lMooD4eaxkxKUCRPJU3k/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QCwkOV6f0fttPF0VyWcMQBNkuV5P2yPb/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jV4FLAPE3Wxky3Y0QHQGLzNOnAZ_gWWa/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rtYLT-hM6PqqK3iD8LDVYpSSPE6Ws-Xy/view?usp=share_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UlU6ikz4P4gqbfh5BldP-K_T0lNftMBO/view?usp=share_link</t>
   </si>
 </sst>
 </file>
@@ -4039,6 +4537,14 @@
 </file>
 
 <file path=xl/persons/person2.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person3.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person4.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -12724,7 +13230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G317"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -15742,7 +16248,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>45025</v>
       </c>
@@ -15753,7 +16259,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>45025</v>
       </c>
@@ -15764,7 +16270,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>45025</v>
       </c>
@@ -15775,7 +16281,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>45025</v>
       </c>
@@ -15786,7 +16292,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>45025</v>
       </c>
@@ -15797,7 +16303,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>45025</v>
       </c>
@@ -15808,7 +16314,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>45025</v>
       </c>
@@ -15819,7 +16325,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>45025</v>
       </c>
@@ -15830,7 +16336,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>45025</v>
       </c>
@@ -15841,7 +16347,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>45025</v>
       </c>
@@ -15852,466 +16358,367 @@
         <v>895</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B283" s="2">
         <v>1</v>
       </c>
       <c r="C283" t="s">
-        <v>1224</v>
-      </c>
-      <c r="G283" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B284" s="2">
         <v>2</v>
       </c>
       <c r="C284" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G284" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B285" s="2">
         <v>3</v>
       </c>
       <c r="C285" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G285" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B286" s="2">
         <v>4</v>
       </c>
       <c r="C286" t="s">
-        <v>1227</v>
-      </c>
-      <c r="G286" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B287" s="2">
         <v>5</v>
       </c>
       <c r="C287" t="s">
-        <v>1228</v>
-      </c>
-      <c r="G287" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B288" s="2">
         <v>6</v>
       </c>
       <c r="C288" t="s">
-        <v>1229</v>
-      </c>
-      <c r="G288" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B289" s="2">
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>1230</v>
-      </c>
-      <c r="G289" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B290" s="2">
         <v>8</v>
       </c>
       <c r="C290" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G290" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B291" s="2">
         <v>9</v>
       </c>
       <c r="C291" t="s">
-        <v>1232</v>
-      </c>
-      <c r="G291" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B292" s="2">
         <v>10</v>
       </c>
       <c r="C292" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G292" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B293" s="2">
         <v>11</v>
       </c>
       <c r="C293" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G293" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B294" s="2">
         <v>12</v>
       </c>
       <c r="C294" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G294" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B295" s="2">
         <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G295" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B296" s="2">
         <v>14</v>
       </c>
       <c r="C296" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G296" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B297" s="2">
         <v>15</v>
       </c>
       <c r="C297" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G297" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B298" s="2">
         <v>16</v>
       </c>
       <c r="C298" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G298" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B299" s="2">
         <v>17</v>
       </c>
       <c r="C299" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G299" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B300" s="2">
         <v>18</v>
       </c>
       <c r="C300" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G300" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B301" s="2">
         <v>19</v>
       </c>
       <c r="C301" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G301" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B302" s="2">
         <v>20</v>
       </c>
       <c r="C302" t="s">
-        <v>1243</v>
-      </c>
-      <c r="G302" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B303" s="2">
         <v>21</v>
       </c>
       <c r="C303" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G303" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B304" s="2">
         <v>22</v>
       </c>
       <c r="C304" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G304" t="s">
-        <v>1278</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B305" s="2">
         <v>23</v>
       </c>
       <c r="C305" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G305" t="s">
-        <v>1277</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B306" s="2">
         <v>24</v>
       </c>
       <c r="C306" t="s">
-        <v>1247</v>
-      </c>
-      <c r="G306" t="s">
-        <v>1276</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B307" s="2">
         <v>25</v>
       </c>
       <c r="C307" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G307" t="s">
-        <v>1275</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B308" s="2">
         <v>26</v>
       </c>
       <c r="C308" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G308" t="s">
-        <v>1274</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B309" s="2">
         <v>27</v>
       </c>
       <c r="C309" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G309" t="s">
-        <v>1273</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B310" s="2">
         <v>28</v>
       </c>
       <c r="C310" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G310" t="s">
-        <v>1272</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B311" s="2">
         <v>29</v>
       </c>
       <c r="C311" t="s">
-        <v>1252</v>
-      </c>
-      <c r="G311" t="s">
-        <v>1271</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B312" s="2">
         <v>30</v>
       </c>
       <c r="C312" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G312" t="s">
-        <v>1270</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B313" s="2">
         <v>31</v>
       </c>
       <c r="C313" t="s">
-        <v>1254</v>
-      </c>
-      <c r="G313" t="s">
-        <v>1269</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B314" s="2">
         <v>32</v>
       </c>
       <c r="C314" t="s">
-        <v>1255</v>
-      </c>
-      <c r="G314" t="s">
-        <v>1268</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
-        <v>45027</v>
+        <v>45026</v>
       </c>
       <c r="B315" s="2">
         <v>33</v>
       </c>
       <c r="C315" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G315" t="s">
-        <v>1267</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -16319,13 +16726,13 @@
         <v>45027</v>
       </c>
       <c r="B316" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C316" t="s">
-        <v>1257</v>
+        <v>1224</v>
       </c>
       <c r="G316" t="s">
-        <v>1266</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -16333,17 +16740,1421 @@
         <v>45027</v>
       </c>
       <c r="B317" s="2">
+        <v>2</v>
+      </c>
+      <c r="C317" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G317" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A318" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B318" s="2">
+        <v>3</v>
+      </c>
+      <c r="C318" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G318" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A319" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B319" s="2">
+        <v>4</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G319" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A320" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B320" s="2">
+        <v>5</v>
+      </c>
+      <c r="C320" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G320" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A321" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B321" s="2">
+        <v>6</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G321" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A322" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B322" s="2">
+        <v>7</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G322" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A323" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B323" s="2">
+        <v>8</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G323" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A324" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B324" s="2">
+        <v>9</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G324" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A325" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B325" s="2">
+        <v>10</v>
+      </c>
+      <c r="C325" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G325" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A326" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B326" s="2">
+        <v>11</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G326" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A327" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B327" s="2">
+        <v>12</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G327" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A328" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B328" s="2">
+        <v>13</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G328" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A329" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B329" s="2">
+        <v>14</v>
+      </c>
+      <c r="C329" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G329" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A330" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B330" s="2">
+        <v>15</v>
+      </c>
+      <c r="C330" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G330" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A331" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B331" s="2">
+        <v>16</v>
+      </c>
+      <c r="C331" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G331" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A332" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B332" s="2">
+        <v>17</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G332" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A333" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B333" s="2">
+        <v>18</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G333" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A334" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B334" s="2">
+        <v>19</v>
+      </c>
+      <c r="C334" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G334" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A335" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B335" s="2">
+        <v>20</v>
+      </c>
+      <c r="C335" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G335" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A336" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B336" s="2">
+        <v>21</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G336" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A337" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B337" s="2">
+        <v>22</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G337" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A338" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B338" s="2">
+        <v>23</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G338" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A339" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B339" s="2">
+        <v>24</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G339" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A340" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B340" s="2">
+        <v>25</v>
+      </c>
+      <c r="C340" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G340" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A341" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B341" s="2">
+        <v>26</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G341" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A342" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B342" s="2">
+        <v>27</v>
+      </c>
+      <c r="C342" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G342" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A343" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B343" s="2">
+        <v>28</v>
+      </c>
+      <c r="C343" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G343" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A344" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B344" s="2">
+        <v>29</v>
+      </c>
+      <c r="C344" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G344" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A345" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B345" s="2">
+        <v>30</v>
+      </c>
+      <c r="C345" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G345" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A346" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B346" s="2">
+        <v>31</v>
+      </c>
+      <c r="C346" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G346" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A347" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B347" s="2">
+        <v>32</v>
+      </c>
+      <c r="C347" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G347" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A348" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B348" s="2">
+        <v>33</v>
+      </c>
+      <c r="C348" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G348" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A349" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B349" s="2">
+        <v>34</v>
+      </c>
+      <c r="C349" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G349" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A350" s="1">
+        <v>45027</v>
+      </c>
+      <c r="B350" s="2">
         <v>35</v>
       </c>
-      <c r="C317" t="s">
+      <c r="C350" t="s">
         <v>1258</v>
       </c>
-      <c r="G317" t="s">
+      <c r="G350" t="s">
         <v>1265</v>
       </c>
     </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A351" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B351" s="2">
+        <v>1</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G351" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A352" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B352" s="2">
+        <v>2</v>
+      </c>
+      <c r="C352" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G352" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A353" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B353" s="2">
+        <v>3</v>
+      </c>
+      <c r="C353" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G353" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A354" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B354" s="2">
+        <v>4</v>
+      </c>
+      <c r="C354" t="s">
+        <v>948</v>
+      </c>
+      <c r="G354" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A355" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B355" s="2">
+        <v>5</v>
+      </c>
+      <c r="C355" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G355" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A356" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B356" s="2">
+        <v>6</v>
+      </c>
+      <c r="C356" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G356" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A357" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B357" s="2">
+        <v>7</v>
+      </c>
+      <c r="C357" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G357" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A358" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B358" s="2">
+        <v>8</v>
+      </c>
+      <c r="C358" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G358" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A359" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B359" s="2">
+        <v>9</v>
+      </c>
+      <c r="C359" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G359" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A360" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B360" s="2">
+        <v>10</v>
+      </c>
+      <c r="C360" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G360" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A361" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B361" s="2">
+        <v>11</v>
+      </c>
+      <c r="C361" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G361" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A362" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B362" s="2">
+        <v>12</v>
+      </c>
+      <c r="C362" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G362" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B363" s="2">
+        <v>13</v>
+      </c>
+      <c r="C363" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G363" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B364" s="2">
+        <v>14</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G364" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B365" s="2">
+        <v>15</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G365" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B366" s="2">
+        <v>16</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G366" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B367" s="2">
+        <v>17</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G367" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B368" s="2">
+        <v>18</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G368" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B369" s="2">
+        <v>19</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G369" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B370" s="2">
+        <v>20</v>
+      </c>
+      <c r="C370" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G370" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B371" s="2">
+        <v>21</v>
+      </c>
+      <c r="C371" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G371" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A372" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B372" s="2">
+        <v>22</v>
+      </c>
+      <c r="C372" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G372" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B373" s="2">
+        <v>23</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G373" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B374" s="2">
+        <v>24</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G374" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B375" s="2">
+        <v>25</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G375" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B376" s="2">
+        <v>26</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G376" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B377" s="2">
+        <v>27</v>
+      </c>
+      <c r="C377" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G377" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B378" s="2">
+        <v>28</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G378" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B379" s="2">
+        <v>29</v>
+      </c>
+      <c r="C379" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G379" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B380" s="2">
+        <v>30</v>
+      </c>
+      <c r="C380" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G380" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B381" s="2">
+        <v>31</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G381" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B382" s="2">
+        <v>32</v>
+      </c>
+      <c r="C382" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G382" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B383" s="2">
+        <v>33</v>
+      </c>
+      <c r="C383" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G383" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B384" s="2">
+        <v>1</v>
+      </c>
+      <c r="C384" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G384" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B385" s="2">
+        <v>2</v>
+      </c>
+      <c r="C385" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G385" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B386" s="2">
+        <v>3</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G386" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B387" s="2">
+        <v>4</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G387" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B388" s="2">
+        <v>5</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G388" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B389" s="2">
+        <v>6</v>
+      </c>
+      <c r="C389" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G389" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B390" s="2">
+        <v>7</v>
+      </c>
+      <c r="C390" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G390" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B391" s="2">
+        <v>8</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G391" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B392" s="2">
+        <v>9</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G392" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B393" s="2">
+        <v>10</v>
+      </c>
+      <c r="C393" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G393" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B394" s="2">
+        <v>11</v>
+      </c>
+      <c r="C394" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G394" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B395" s="2">
+        <v>12</v>
+      </c>
+      <c r="C395" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G395" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B396" s="2">
+        <v>13</v>
+      </c>
+      <c r="C396" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G396" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B397" s="2">
+        <v>14</v>
+      </c>
+      <c r="C397" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G397" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B398" s="2">
+        <v>15</v>
+      </c>
+      <c r="C398" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G398" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B399" s="2">
+        <v>16</v>
+      </c>
+      <c r="C399" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G399" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B400" s="2">
+        <v>17</v>
+      </c>
+      <c r="C400" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G400" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B401" s="2">
+        <v>18</v>
+      </c>
+      <c r="C401" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G401" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B402" s="2">
+        <v>19</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G402" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B403" s="2">
+        <v>20</v>
+      </c>
+      <c r="C403" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G403" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A404" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B404" s="2">
+        <v>21</v>
+      </c>
+      <c r="C404" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G404" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A405" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B405" s="2">
+        <v>22</v>
+      </c>
+      <c r="C405" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G405" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B406" s="2">
+        <v>23</v>
+      </c>
+      <c r="C406" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G406" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B407" s="2">
+        <v>24</v>
+      </c>
+      <c r="C407" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G407" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B408" s="2">
+        <v>25</v>
+      </c>
+      <c r="C408" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G408" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B409" s="2">
+        <v>26</v>
+      </c>
+      <c r="C409" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G409" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B410" s="2">
+        <v>27</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G410" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A411" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B411" s="2">
+        <v>28</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G411" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A412" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B412" s="2">
+        <v>29</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G412" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A413" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B413" s="2">
+        <v>30</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G413" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A414" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B414" s="2">
+        <v>31</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G414" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A415" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B415" s="2">
+        <v>32</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G415" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A416" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B416" s="2">
+        <v>33</v>
+      </c>
+      <c r="C416" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G416" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A417" s="1">
+        <v>45029</v>
+      </c>
+      <c r="B417" s="2">
+        <v>34</v>
+      </c>
+      <c r="C417" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G417" t="s">
+        <v>1432</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G383">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{30EA2378-418A-4D44-A1A7-FD4261291C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14FBF26-E233-48BB-AB6E-B205375A98C1}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{30EA2378-418A-4D44-A1A7-FD4261291C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D827894-2335-4C21-B70F-B8A6B9DC2144}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January 2022" sheetId="3" r:id="rId1"/>
@@ -28,6 +28,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'April 2023'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'August 2022'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'July 2022'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'March 2023'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'October 2022'!$A$1:$G$1</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="2014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="2078">
   <si>
     <t>Unhappy nation</t>
   </si>
@@ -5075,9 +5076,6 @@
     <t>What draft Bill on regulating medical devices says, and what it does not</t>
   </si>
   <si>
-    <t>The should be no curbs on deliberation</t>
-  </si>
-  <si>
     <t>Reading the population</t>
   </si>
   <si>
@@ -5246,9 +5244,6 @@
     <t>Put nature at the heart of economic policies</t>
   </si>
   <si>
-    <t>The incredible Green Hydrogen</t>
-  </si>
-  <si>
     <t>Need to link small and large businesses</t>
   </si>
   <si>
@@ -5258,9 +5253,6 @@
     <t>A new judicial device for 'complete justice'</t>
   </si>
   <si>
-    <t>The sale of municipal fiances in inadequate</t>
-  </si>
-  <si>
     <t>Create more jobs, revamp employment policy</t>
   </si>
   <si>
@@ -5987,9 +5979,6 @@
     <t>Focus of securities market rules must change</t>
   </si>
   <si>
-    <t>Why is defection a non-issue for voters</t>
-  </si>
-  <si>
     <t>The functioning of National Investigation Agency</t>
   </si>
   <si>
@@ -6093,13 +6082,217 @@
   </si>
   <si>
     <t>Battle for the Black Sea</t>
+  </si>
+  <si>
+    <t>India needs to science things up</t>
+  </si>
+  <si>
+    <t>When bulldozers threaten democracy</t>
+  </si>
+  <si>
+    <t>Drug resistance may spawn new diseases</t>
+  </si>
+  <si>
+    <t>A new bipolar future</t>
+  </si>
+  <si>
+    <t>108 &amp; 104 totally dissimilar services</t>
+  </si>
+  <si>
+    <t>Why is defection a non-issue for voters?</t>
+  </si>
+  <si>
+    <t>We need an urgent national plan on electrical safety</t>
+  </si>
+  <si>
+    <t>Technology is no panacea for custodial deaths</t>
+  </si>
+  <si>
+    <t>Farm reforms need a GST-like council</t>
+  </si>
+  <si>
+    <t>Prerequisites for dynamic spectrum access</t>
+  </si>
+  <si>
+    <t>Forget Web3. India is miles ahead with its UPI</t>
+  </si>
+  <si>
+    <t>Risks in Cyber Space</t>
+  </si>
+  <si>
+    <t>What GST rate changes mean</t>
+  </si>
+  <si>
+    <t>Right intent, confusing content</t>
+  </si>
+  <si>
+    <t>Are India's forex reserves adequate?</t>
+  </si>
+  <si>
+    <t>Dealing with effects of stunted farm sector</t>
+  </si>
+  <si>
+    <t>Mode of managing CSS funds should change</t>
+  </si>
+  <si>
+    <t>Are we squandering our democracy?</t>
+  </si>
+  <si>
+    <t>The dark side of sharing</t>
+  </si>
+  <si>
+    <t>Legal panacea for ills of sex workers</t>
+  </si>
+  <si>
+    <t>Degrees of privacy and freedom</t>
+  </si>
+  <si>
+    <t>How AI and advanced analytics have begun transforming M&amp;As</t>
+  </si>
+  <si>
+    <t>The need for space sustainability</t>
+  </si>
+  <si>
+    <t>A regulatory framework for digital assets in India</t>
+  </si>
+  <si>
+    <t>Disqualification due to defection</t>
+  </si>
+  <si>
+    <t>India needs special drive for quality jobs for female workforce</t>
+  </si>
+  <si>
+    <t>Rule of law, anyone?</t>
+  </si>
+  <si>
+    <t>The incredible Green Hydro Hub</t>
+  </si>
+  <si>
+    <t>The scale of municipal finances in inadequate</t>
+  </si>
+  <si>
+    <t>There should be no curbs on deliberation</t>
+  </si>
+  <si>
+    <t>Did Sweden's open Covid policy work?</t>
+  </si>
+  <si>
+    <t>India@75: Unshackle political bondages</t>
+  </si>
+  <si>
+    <t>Urbanisations's different strokes</t>
+  </si>
+  <si>
+    <t>Indian philanthropy has a worthy record that could shine brighter</t>
+  </si>
+  <si>
+    <t>Meet the promise of education: It's a national imperative</t>
+  </si>
+  <si>
+    <t>Tackle conflict with joint politico-military approach</t>
+  </si>
+  <si>
+    <t>Preventing the slide in criminal justice system</t>
+  </si>
+  <si>
+    <t>I2U2 opens new doors</t>
+  </si>
+  <si>
+    <t>The 'developed country' goal</t>
+  </si>
+  <si>
+    <t>A modest agenda for reform</t>
+  </si>
+  <si>
+    <t>What is causing Arctic warming?</t>
+  </si>
+  <si>
+    <t>The Centre vs State tussle over IAS postings</t>
+  </si>
+  <si>
+    <t>Data opportunity at the G20</t>
+  </si>
+  <si>
+    <t>This maritime partnership is still a work in progress</t>
+  </si>
+  <si>
+    <t>Beacon of hope</t>
+  </si>
+  <si>
+    <t>Selling public sector banks is no solution</t>
+  </si>
+  <si>
+    <t>An enforceable global law needed to curb terrorism</t>
+  </si>
+  <si>
+    <t>The value of dissent</t>
+  </si>
+  <si>
+    <t>GST hurting key sectors</t>
+  </si>
+  <si>
+    <t>The Bilkis case remissions</t>
+  </si>
+  <si>
+    <t>Power, a reality check</t>
+  </si>
+  <si>
+    <t>Condemn, and listen</t>
+  </si>
+  <si>
+    <t>Presumed guilty</t>
+  </si>
+  <si>
+    <t>History of strategic thinking on the Indo-Pacific</t>
+  </si>
+  <si>
+    <t>The amnesia of Western violence</t>
+  </si>
+  <si>
+    <t>Impart knowledge with holistic education</t>
+  </si>
+  <si>
+    <t>A route to reform</t>
+  </si>
+  <si>
+    <t>Clinging on to ivory tower?</t>
+  </si>
+  <si>
+    <t>The Social Dilemma of personal data</t>
+  </si>
+  <si>
+    <t>Bhawani Mandir revisited: Sri Aurobindo &amp; Swaraj</t>
+  </si>
+  <si>
+    <t>A probe into the Nehruvian pledge</t>
+  </si>
+  <si>
+    <t>The coming 75 years</t>
+  </si>
+  <si>
+    <t>Stepping back from an ecological abyss</t>
+  </si>
+  <si>
+    <t>High points in science, technology and innovation</t>
+  </si>
+  <si>
+    <t>The Capital Question</t>
+  </si>
+  <si>
+    <t>Bureaucrats haven't failed. But they can do better</t>
+  </si>
+  <si>
+    <t>The G20 presidency will offer us a chance to pursue our ambitions</t>
+  </si>
+  <si>
+    <t>Unlocking the promise of blended finance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6128,6 +6321,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6149,7 +6348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6163,6 +6362,8 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6201,6 +6402,14 @@
 </file>
 
 <file path=xl/persons/person4.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person5.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person6.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -20456,7 +20665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{082CD2CE-A2C7-4EAE-AD94-B46F5A55B5FE}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -20488,6 +20697,36 @@
         <v>1256</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>1972</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20495,7 +20734,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEA76CE5-F791-4FEE-B1E7-C53D2A314375}">
-  <dimension ref="A1:G343"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -20528,69 +20767,135 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2" t="s">
-        <v>1845</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3" t="s">
-        <v>1917</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
       <c r="C4" t="s">
-        <v>1691</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
       <c r="C5" t="s">
-        <v>1962</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
       <c r="C6" t="s">
-        <v>1973</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
       <c r="C7" t="s">
-        <v>1958</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
       <c r="C8" t="s">
-        <v>1715</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
       <c r="C9" t="s">
-        <v>1734</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
       <c r="C10" t="s">
-        <v>1757</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
       <c r="C11" t="s">
-        <v>1894</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
       <c r="C12" t="s">
-        <v>1683</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>44744</v>
+        <v>44743</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>2003</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -20598,1949 +20903,3239 @@
         <v>44743</v>
       </c>
       <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B15">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
         <v>1993</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>1821</v>
-      </c>
-    </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
       <c r="C20" t="s">
-        <v>1909</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
       <c r="C21" t="s">
-        <v>1701</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
       <c r="C22" t="s">
-        <v>1859</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
       <c r="C23" t="s">
-        <v>1891</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
       <c r="C24" t="s">
-        <v>1770</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>44744</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
       <c r="C25" t="s">
-        <v>1945</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
       <c r="C26" t="s">
-        <v>1843</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
       <c r="C27" t="s">
-        <v>1817</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
       <c r="C28" t="s">
-        <v>1698</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
       <c r="C29" t="s">
-        <v>1934</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>44743</v>
+        <v>44745</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>1987</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
       <c r="C31" t="s">
-        <v>1849</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
       <c r="C32" t="s">
-        <v>1853</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B33" s="8">
+        <v>44745</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>44745</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B40">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B45">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B46">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B48">
         <v>13</v>
       </c>
-      <c r="C33" t="s">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C35" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C37" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C38" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C39" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C41" t="s">
-        <v>1819</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C42" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C43" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C44" t="s">
-        <v>1798</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C45" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C46" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C47" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>1703</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B49">
+        <v>14</v>
+      </c>
       <c r="C49" t="s">
-        <v>1714</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
       <c r="C50" t="s">
-        <v>1688</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
       <c r="C51" t="s">
-        <v>1846</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
       <c r="C52" t="s">
-        <v>1893</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
       <c r="C53" t="s">
-        <v>1923</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
       <c r="C54" t="s">
-        <v>1758</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
       <c r="C55" t="s">
-        <v>1850</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
       <c r="C56" t="s">
-        <v>1872</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B57" s="8">
-        <v>23</v>
+        <v>44747</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>1676</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B58">
+        <v>9</v>
+      </c>
       <c r="C58" t="s">
-        <v>1724</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
       <c r="C59" t="s">
-        <v>1844</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
       <c r="C60" t="s">
-        <v>1766</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
       <c r="C61" t="s">
-        <v>1955</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
       <c r="C62" t="s">
-        <v>1847</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
       <c r="C63" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B64">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
         <v>1736</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C64" t="s">
-        <v>1825</v>
-      </c>
-    </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B65">
+        <v>6</v>
+      </c>
       <c r="C65" t="s">
-        <v>1899</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B66">
+        <v>7</v>
+      </c>
       <c r="C66" t="s">
-        <v>1776</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>44743</v>
+        <v>44748</v>
       </c>
       <c r="B67">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>1985</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
       <c r="C68" t="s">
-        <v>1900</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B69">
+        <v>10</v>
+      </c>
       <c r="C69" t="s">
-        <v>1807</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B70">
+        <v>11</v>
+      </c>
       <c r="C70" t="s">
-        <v>1965</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
       <c r="C71" t="s">
-        <v>1927</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>44744</v>
+        <v>44748</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>1996</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
       <c r="C73" t="s">
-        <v>1814</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>44744</v>
+        <v>44749</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>1999</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
       <c r="C75" t="s">
-        <v>1753</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>44743</v>
+        <v>44749</v>
       </c>
       <c r="B76">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>1992</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
       <c r="C77" t="s">
-        <v>1704</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B78">
+        <v>4</v>
+      </c>
       <c r="C78" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
       <c r="C79" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>44744</v>
+        <v>44749</v>
       </c>
       <c r="B80">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B81">
+        <v>7</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B82">
+        <v>8</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B83">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B84">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B85">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B86">
+        <v>12</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B87">
+        <v>14</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B89">
         <v>2</v>
       </c>
-      <c r="C80" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C81" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C82" t="s">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C83" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C84" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C85" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C86" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C87" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C88" s="3" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
-        <v>1781</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
+      </c>
       <c r="C90" t="s">
-        <v>1721</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>44743</v>
+        <v>44750</v>
       </c>
       <c r="B91">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>1995</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B92">
+        <v>5</v>
+      </c>
       <c r="C92" t="s">
-        <v>1780</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B93">
+        <v>6</v>
+      </c>
       <c r="C93" t="s">
-        <v>1838</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B94">
+        <v>7</v>
+      </c>
       <c r="C94" t="s">
-        <v>1977</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B95" s="8">
+        <v>44750</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B97">
+        <v>10</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B98">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B100">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B101">
+        <v>14</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>44751</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>44751</v>
+      </c>
+      <c r="B103">
         <v>2</v>
       </c>
-      <c r="C95" t="s">
-        <v>1678</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C96" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C97" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C98" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C99" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C100" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C101" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C102" t="s">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C103" t="s">
-        <v>1903</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <v>44744</v>
+        <v>44751</v>
       </c>
       <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>44751</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>44751</v>
+      </c>
+      <c r="B106">
+        <v>5</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>44751</v>
+      </c>
+      <c r="B107">
         <v>6</v>
       </c>
-      <c r="C104" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C105" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C106" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C107" t="s">
-        <v>1742</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>44751</v>
+      </c>
+      <c r="B108">
+        <v>7</v>
+      </c>
       <c r="C108" t="s">
-        <v>1693</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
       <c r="C109" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
       <c r="C110" t="s">
-        <v>1961</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>44743</v>
+        <v>44752</v>
       </c>
       <c r="B111">
+        <v>3</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B112">
+        <v>5</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B113">
+        <v>6</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B114">
+        <v>7</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B115">
+        <v>8</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B116">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>44752</v>
+      </c>
+      <c r="B117">
+        <v>10</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B118">
         <v>1</v>
       </c>
-      <c r="C111" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C112" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C113" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C114" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C115" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C116" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C117" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C118" t="s">
-        <v>1905</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>44743</v>
+        <v>44753</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>1983</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>44744</v>
+        <v>44753</v>
       </c>
       <c r="B120">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B122">
         <v>5</v>
       </c>
-      <c r="C120" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C121" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C122" t="s">
-        <v>1826</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B123">
+        <v>6</v>
+      </c>
       <c r="C123" t="s">
-        <v>1868</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B124">
+        <v>7</v>
+      </c>
       <c r="C124" t="s">
-        <v>1836</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>44743</v>
+        <v>44753</v>
       </c>
       <c r="B125">
+        <v>8</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B126">
+        <v>9</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B127">
         <v>10</v>
       </c>
-      <c r="C125" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C126" t="s">
-        <v>1769</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C127" t="s">
-        <v>1851</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B128">
+        <v>11</v>
+      </c>
       <c r="C128" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>44753</v>
+      </c>
+      <c r="B129">
+        <v>12</v>
+      </c>
       <c r="C129" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
       <c r="C130" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
       <c r="C131" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B132">
+        <v>3</v>
+      </c>
       <c r="C132" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
       <c r="C133" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
       <c r="C134" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B135">
+        <v>6</v>
+      </c>
       <c r="C135" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B136">
+        <v>7</v>
+      </c>
       <c r="C136" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
       <c r="C137" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B138">
+        <v>9</v>
+      </c>
       <c r="C138" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B139">
+        <v>10</v>
+      </c>
       <c r="C139" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B140">
+        <v>11</v>
+      </c>
       <c r="C140" t="s">
-        <v>1839</v>
-      </c>
-    </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B141">
+        <v>12</v>
+      </c>
       <c r="C141" t="s">
-        <v>1858</v>
-      </c>
-    </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B142">
+        <v>13</v>
+      </c>
       <c r="C142" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B143">
+        <v>14</v>
+      </c>
       <c r="C143" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B144">
+        <v>15</v>
+      </c>
       <c r="C144" t="s">
-        <v>1841</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B145">
+        <v>16</v>
+      </c>
       <c r="C145" t="s">
-        <v>1707</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B146">
+        <v>17</v>
+      </c>
       <c r="C146" t="s">
-        <v>1744</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>44754</v>
+      </c>
+      <c r="B147">
+        <v>18</v>
+      </c>
       <c r="C147" t="s">
-        <v>1959</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>44743</v>
+        <v>44754</v>
       </c>
       <c r="B148">
+        <v>19</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B151">
+        <v>3</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B152">
+        <v>4</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B153">
+        <v>5</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B154">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B155">
+        <v>7</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B156">
+        <v>8</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B157">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B158">
+        <v>10</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B159">
         <v>11</v>
       </c>
-      <c r="C148" t="s">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C149" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C150" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C151" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C152" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C153" t="s">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C154" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C155" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C156" t="s">
-        <v>1832</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C157" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C158" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
-        <v>1762</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B160">
+        <v>12</v>
+      </c>
       <c r="C160" t="s">
-        <v>1748</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B161" s="8">
-        <v>15</v>
+        <v>44755</v>
+      </c>
+      <c r="B161">
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>1879</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
       <c r="C162" t="s">
-        <v>1957</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
       <c r="C163" t="s">
-        <v>1708</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B164">
+        <v>3</v>
+      </c>
       <c r="C164" t="s">
-        <v>1739</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
       <c r="C165" t="s">
-        <v>1916</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B166">
+        <v>5</v>
+      </c>
       <c r="C166" t="s">
-        <v>1784</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B167">
+        <v>6</v>
+      </c>
       <c r="C167" t="s">
-        <v>1774</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B168">
+        <v>7</v>
+      </c>
       <c r="C168" t="s">
-        <v>1728</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B169">
+        <v>8</v>
+      </c>
       <c r="C169" t="s">
-        <v>1935</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B170">
+        <v>9</v>
+      </c>
       <c r="C170" t="s">
-        <v>1890</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B171">
+        <v>10</v>
+      </c>
       <c r="C171" t="s">
-        <v>1968</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
       <c r="C172" t="s">
-        <v>1723</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
       <c r="C173" t="s">
-        <v>1940</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C174" t="s">
-        <v>1953</v>
+      <c r="A174" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B174">
+        <v>3</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B175">
+        <v>4</v>
+      </c>
       <c r="C175" t="s">
-        <v>1761</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B176">
+        <v>5</v>
+      </c>
       <c r="C176" t="s">
-        <v>1702</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B177">
+        <v>6</v>
+      </c>
       <c r="C177" t="s">
-        <v>1896</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B178">
+        <v>7</v>
+      </c>
       <c r="C178" t="s">
-        <v>1732</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B179">
+        <v>8</v>
+      </c>
       <c r="C179" t="s">
-        <v>1823</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B180">
+        <v>9</v>
+      </c>
       <c r="C180" t="s">
-        <v>1828</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B181">
+        <v>10</v>
+      </c>
       <c r="C181" t="s">
-        <v>1777</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B182">
+        <v>11</v>
+      </c>
       <c r="C182" t="s">
-        <v>1794</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B183">
+        <v>12</v>
+      </c>
       <c r="C183" t="s">
-        <v>1947</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
       <c r="C184" t="s">
-        <v>1740</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
       <c r="C185" t="s">
-        <v>1760</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B186" s="8">
-        <v>29</v>
+        <v>44758</v>
+      </c>
+      <c r="B186">
+        <v>3</v>
       </c>
       <c r="C186" t="s">
-        <v>1881</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
-        <v>44744</v>
+        <v>44758</v>
       </c>
       <c r="B187">
+        <v>4</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B188">
+        <v>5</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B189">
+        <v>6</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B190">
         <v>7</v>
       </c>
-      <c r="C187" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C188" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C189" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
-        <v>1880</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B191">
+        <v>8</v>
+      </c>
       <c r="C191" t="s">
-        <v>1782</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B192">
+        <v>9</v>
+      </c>
       <c r="C192" t="s">
-        <v>1689</v>
-      </c>
-    </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B193">
+        <v>10</v>
+      </c>
       <c r="C193" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B194">
+        <v>11</v>
+      </c>
       <c r="C194" t="s">
-        <v>1822</v>
-      </c>
-    </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B195">
+        <v>12</v>
+      </c>
       <c r="C195" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B196">
+        <v>1</v>
+      </c>
       <c r="C196" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B197">
+        <v>2</v>
+      </c>
       <c r="C197" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B198">
+        <v>3</v>
+      </c>
       <c r="C198" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B199">
+        <v>4</v>
+      </c>
       <c r="C199" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B200">
+        <v>5</v>
+      </c>
       <c r="C200" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B201">
+        <v>6</v>
+      </c>
       <c r="C201" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B202">
+        <v>7</v>
+      </c>
       <c r="C202" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B203">
+        <v>8</v>
+      </c>
       <c r="C203" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B204">
+        <v>9</v>
+      </c>
       <c r="C204" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B205">
+        <v>10</v>
+      </c>
       <c r="C205" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C206" s="3" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B206">
+        <v>11</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>44759</v>
+      </c>
+      <c r="B207">
+        <v>12</v>
+      </c>
       <c r="C207" t="s">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
       <c r="C208" t="s">
-        <v>1730</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B209">
+        <v>2</v>
+      </c>
       <c r="C209" t="s">
-        <v>1883</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B210">
+        <v>3</v>
+      </c>
       <c r="C210" t="s">
-        <v>1820</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B211" s="8">
+        <v>44760</v>
+      </c>
+      <c r="B211" s="9">
+        <v>4</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B212">
         <v>5</v>
       </c>
-      <c r="C211" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C212" t="s">
-        <v>1752</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B213">
+        <v>6</v>
+      </c>
       <c r="C213" t="s">
-        <v>1929</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B214">
+        <v>7</v>
+      </c>
       <c r="C214" t="s">
-        <v>1919</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B215" s="9">
+        <v>8</v>
+      </c>
       <c r="C215" t="s">
-        <v>1857</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B216" s="9">
+        <v>9</v>
+      </c>
       <c r="C216" t="s">
-        <v>1729</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B217" s="9">
+        <v>10</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B218">
+        <v>11</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B219" s="9">
+        <v>12</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B220" s="9">
+        <v>13</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B221">
+        <v>14</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
         <v>44761</v>
       </c>
-      <c r="B217" s="8">
-        <v>15</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C218" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C219" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C220" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C221" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B222" s="9">
+        <v>1</v>
+      </c>
       <c r="C222" t="s">
-        <v>1933</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
-        <v>44743</v>
+        <v>44761</v>
       </c>
       <c r="B223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C223" t="s">
-        <v>1982</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>44761</v>
       </c>
-      <c r="B224" s="8">
-        <v>1</v>
+      <c r="B224" s="9">
+        <v>3</v>
       </c>
       <c r="C224" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B225">
+        <v>4</v>
+      </c>
       <c r="C225" t="s">
-        <v>1713</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B226" s="8">
-        <v>7</v>
+        <v>44761</v>
+      </c>
+      <c r="B226" s="9">
+        <v>5</v>
       </c>
       <c r="C226" t="s">
         <v>1680</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B227" s="9">
+        <v>6</v>
+      </c>
       <c r="C227" t="s">
-        <v>1936</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B228">
+        <v>7</v>
+      </c>
       <c r="C228" t="s">
-        <v>1738</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B229" s="9">
+        <v>8</v>
+      </c>
       <c r="C229" t="s">
-        <v>1911</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B230">
+        <v>9</v>
+      </c>
       <c r="C230" t="s">
-        <v>1743</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B231" s="9">
+        <v>10</v>
+      </c>
       <c r="C231" t="s">
-        <v>1924</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
-        <v>44743</v>
-      </c>
-      <c r="B232">
-        <v>5</v>
+        <v>44761</v>
+      </c>
+      <c r="B232" s="9">
+        <v>11</v>
       </c>
       <c r="C232" t="s">
-        <v>1984</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B233">
+        <v>12</v>
+      </c>
       <c r="C233" t="s">
-        <v>1720</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B234" s="9">
+        <v>13</v>
+      </c>
       <c r="C234" t="s">
-        <v>1954</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B235">
+        <v>14</v>
+      </c>
       <c r="C235" t="s">
-        <v>1869</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
-        <v>44743</v>
-      </c>
-      <c r="B236">
-        <v>12</v>
+        <v>44761</v>
+      </c>
+      <c r="B236" s="9">
+        <v>15</v>
       </c>
       <c r="C236" t="s">
-        <v>1991</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B237">
+        <v>16</v>
+      </c>
       <c r="C237" t="s">
-        <v>1824</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
       <c r="C238" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B239">
+        <v>2</v>
+      </c>
       <c r="C239" t="s">
-        <v>1737</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B240">
+        <v>3</v>
+      </c>
       <c r="C240" t="s">
-        <v>1884</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
-        <v>44743</v>
+        <v>44762</v>
       </c>
       <c r="B241">
+        <v>4</v>
+      </c>
+      <c r="C241" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B242">
+        <v>5</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B243">
+        <v>6</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B244">
+        <v>7</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B245">
+        <v>8</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B246">
+        <v>9</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B247">
+        <v>10</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B248">
+        <v>11</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B249">
+        <v>12</v>
+      </c>
+      <c r="C249" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B250">
+        <v>13</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B251">
+        <v>14</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B252">
         <v>15</v>
       </c>
-      <c r="C241" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C242" t="s">
-        <v>1834</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C243" t="s">
-        <v>1788</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C244" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C245" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C246" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C247" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C248" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C249" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C250" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C251" t="s">
+      <c r="C252" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B253">
+        <v>1</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B254">
+        <v>2</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B255">
+        <v>3</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B256">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B257">
+        <v>5</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B258">
+        <v>6</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B259">
+        <v>7</v>
+      </c>
+      <c r="C259" t="s">
         <v>1771</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C252" t="s">
-        <v>1906</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C253" t="s">
-        <v>1813</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C254" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C255" t="s">
-        <v>1926</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C256" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C257" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C258" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C259" t="s">
-        <v>1711</v>
-      </c>
-    </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B260">
+        <v>8</v>
+      </c>
       <c r="C260" t="s">
-        <v>1816</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B261">
+        <v>9</v>
+      </c>
       <c r="C261" t="s">
-        <v>1829</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B262">
+        <v>10</v>
+      </c>
       <c r="C262" t="s">
-        <v>1928</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B263">
+        <v>11</v>
+      </c>
       <c r="C263" t="s">
-        <v>1682</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B264">
+        <v>12</v>
+      </c>
       <c r="C264" t="s">
-        <v>1860</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B265">
+        <v>13</v>
+      </c>
       <c r="C265" t="s">
-        <v>1756</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B266" s="8">
-        <v>27</v>
+        <v>44763</v>
+      </c>
+      <c r="B266">
+        <v>14</v>
       </c>
       <c r="C266" t="s">
-        <v>1901</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>44763</v>
+      </c>
+      <c r="B267">
+        <v>15</v>
+      </c>
       <c r="C267" t="s">
-        <v>1804</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B268">
+        <v>1</v>
+      </c>
       <c r="C268" t="s">
-        <v>1854</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B269">
+        <v>2</v>
+      </c>
       <c r="C269" t="s">
-        <v>1863</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B270">
+        <v>3</v>
+      </c>
       <c r="C270" t="s">
-        <v>1907</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B271">
+        <v>4</v>
+      </c>
       <c r="C271" t="s">
-        <v>1735</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B272">
+        <v>5</v>
+      </c>
       <c r="C272" t="s">
-        <v>1830</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B273">
+        <v>6</v>
+      </c>
       <c r="C273" t="s">
-        <v>1815</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B274">
+        <v>7</v>
+      </c>
       <c r="C274" t="s">
-        <v>1938</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B275">
+        <v>8</v>
+      </c>
       <c r="C275" t="s">
-        <v>1685</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B276" s="8">
-        <v>25</v>
+        <v>44764</v>
+      </c>
+      <c r="B276">
+        <v>9</v>
       </c>
       <c r="C276" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
-        <v>44760</v>
-      </c>
-      <c r="B277" s="8">
-        <v>5</v>
+        <v>44764</v>
+      </c>
+      <c r="B277">
+        <v>10</v>
       </c>
       <c r="C277" t="s">
-        <v>1873</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
-        <v>44744</v>
+        <v>44764</v>
       </c>
       <c r="B278">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C278" t="s">
-        <v>1998</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B279">
+        <v>12</v>
+      </c>
       <c r="C279" t="s">
-        <v>1837</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>44764</v>
+      </c>
+      <c r="B280">
+        <v>13</v>
+      </c>
       <c r="C280" t="s">
-        <v>1764</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B281">
+        <v>1</v>
+      </c>
       <c r="C281" t="s">
-        <v>1864</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
-        <v>44743</v>
+        <v>44765</v>
       </c>
       <c r="B282">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C282" t="s">
-        <v>1986</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B283">
+        <v>3</v>
+      </c>
       <c r="C283" t="s">
-        <v>1741</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B284">
+        <v>4</v>
+      </c>
       <c r="C284" t="s">
-        <v>1768</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B285">
+        <v>5</v>
+      </c>
       <c r="C285" t="s">
-        <v>1791</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B286" s="8">
+        <v>44765</v>
+      </c>
+      <c r="B286">
+        <v>6</v>
+      </c>
+      <c r="C286" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B287">
         <v>7</v>
       </c>
-      <c r="C286" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C287" t="s">
-        <v>1835</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
-        <v>44743</v>
+        <v>44765</v>
       </c>
       <c r="B288">
+        <v>8</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B289">
         <v>9</v>
       </c>
-      <c r="C288" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C289" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B290">
+        <v>10</v>
+      </c>
       <c r="C290" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B291">
+        <v>11</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B292">
+        <v>12</v>
+      </c>
+      <c r="C292" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C291" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C292" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B293">
+        <v>13</v>
+      </c>
       <c r="C293" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B294">
+        <v>14</v>
+      </c>
       <c r="C294" t="s">
-        <v>1812</v>
-      </c>
-    </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B295">
+        <v>15</v>
+      </c>
       <c r="C295" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B296">
+        <v>16</v>
+      </c>
       <c r="C296" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>44765</v>
+      </c>
+      <c r="B297">
+        <v>17</v>
+      </c>
       <c r="C297" t="s">
-        <v>1789</v>
-      </c>
-    </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
       <c r="C298" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B299">
+        <v>2</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B300">
+        <v>3</v>
+      </c>
+      <c r="C300" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B301">
+        <v>4</v>
+      </c>
+      <c r="C301" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B302">
+        <v>5</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B303">
+        <v>6</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B304">
+        <v>7</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B305">
+        <v>8</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B306">
+        <v>9</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>44766</v>
+      </c>
+      <c r="B307">
+        <v>10</v>
+      </c>
+      <c r="C307" t="s">
         <v>1719</v>
-      </c>
-    </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C299" t="s">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C300" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C301" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C302" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C303" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C304" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C305" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C306" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C307" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C308" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C309" t="s">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C310" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C311" t="s">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B312" s="8">
-        <v>10</v>
-      </c>
-      <c r="C312" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C313" t="s">
-        <v>1810</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C314" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A315" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B315" s="8">
-        <v>7</v>
-      </c>
-      <c r="C315" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C316" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C317" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C318" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C319" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C320" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C321" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C322" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C323" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C324" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C325" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C326" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C327" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A328" s="1">
-        <v>44743</v>
-      </c>
-      <c r="B328">
-        <v>2</v>
-      </c>
-      <c r="C328" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C329" t="s">
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C330" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C331" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C332" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A333" s="1">
-        <v>44761</v>
-      </c>
-      <c r="B333" s="8">
-        <v>29</v>
-      </c>
-      <c r="C333" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A334" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B334">
-        <v>1</v>
-      </c>
-      <c r="C334" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A335" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B335">
-        <v>2</v>
-      </c>
-      <c r="C335" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A336" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B336">
-        <v>3</v>
-      </c>
-      <c r="C336" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B337">
-        <v>4</v>
-      </c>
-      <c r="C337" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B338">
-        <v>5</v>
-      </c>
-      <c r="C338" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B339">
-        <v>6</v>
-      </c>
-      <c r="C339" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A340" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B340">
-        <v>7</v>
-      </c>
-      <c r="C340" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B341">
-        <v>8</v>
-      </c>
-      <c r="C341" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A342" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B342">
-        <v>9</v>
-      </c>
-      <c r="C342" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" s="1">
-        <v>44745</v>
-      </c>
-      <c r="B343">
-        <v>10</v>
-      </c>
-      <c r="C343" t="s">
-        <v>2013</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{CEA76CE5-F791-4FEE-B1E7-C53D2A314375}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G333">
-      <sortCondition ref="C1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G369">
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22550,7 +24145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A74BAF-B28C-43A3-89C1-49099F33BB50}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -22582,7 +24177,1046 @@
         <v>1256</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>44786</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>44787</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B34">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B38">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B39">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B40">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B41">
+        <v>14</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B44">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B45">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B46">
+        <v>19</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B47">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>44788</v>
+      </c>
+      <c r="B48">
+        <v>21</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B55">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B56">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B57">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>44789</v>
+      </c>
+      <c r="B59">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B64">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B65">
+        <v>6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B66">
+        <v>7</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B67">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B69">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B70">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B72">
+        <v>13</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B74">
+        <v>15</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>44791</v>
+      </c>
+      <c r="B75">
+        <v>16</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B80">
+        <v>5</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B81">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B82">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B83">
+        <v>8</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B84">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B85">
+        <v>10</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B86">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B87">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B88">
+        <v>13</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B89">
+        <v>14</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B90">
+        <v>15</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B91">
+        <v>16</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B92">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B93">
+        <v>18</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B94">
+        <v>19</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>44800</v>
+      </c>
+      <c r="B95">
+        <v>20</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2077</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{C7A74BAF-B28C-43A3-89C1-49099F33BB50}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G95">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maadh\OneDrive\Desktop\serveup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{CF621C43-08FE-4645-B08B-F30FFFCC1169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52434D1C-21EF-46BC-ABAA-8F19B5224D5E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838EEE59-42EF-4602-B9DC-DAB7C90AD36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="405" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="405" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January 2022" sheetId="3" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6299" uniqueCount="5274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6385" uniqueCount="5360">
   <si>
     <t>Unhappy nation</t>
   </si>
@@ -15881,6 +15881,264 @@
   </si>
   <si>
     <t>Don't privilege govt workers over others</t>
+  </si>
+  <si>
+    <t>Pak's terror factory is exposing SCO's limits</t>
+  </si>
+  <si>
+    <t>Unfolding crisis</t>
+  </si>
+  <si>
+    <t>Nations must shun urge to dominate</t>
+  </si>
+  <si>
+    <t>The other Thucydides trap</t>
+  </si>
+  <si>
+    <t>AI regulation is key to free-rider problem</t>
+  </si>
+  <si>
+    <t>India's moment in geopolitics at SCO meets</t>
+  </si>
+  <si>
+    <t>Double standards of criminal court</t>
+  </si>
+  <si>
+    <t>Why Shimla was chosen as capital</t>
+  </si>
+  <si>
+    <t>KCR proves confidence &amp; fortitude lead to success</t>
+  </si>
+  <si>
+    <t>ChatGPT raises data theft, hacking risks multi-fold</t>
+  </si>
+  <si>
+    <t>India lost land at LAC, step up strategic game</t>
+  </si>
+  <si>
+    <t>Scientists help find new kind of molecular motor</t>
+  </si>
+  <si>
+    <t>Mixing caste &amp; sports shames 'Bhavya Bharat'</t>
+  </si>
+  <si>
+    <t>From basic structure to collegium: A shared thread</t>
+  </si>
+  <si>
+    <t>Time for smashing stereotypes about singlehood</t>
+  </si>
+  <si>
+    <t>For politicians, age is just a number</t>
+  </si>
+  <si>
+    <t>A stronger Global South can usher in prosperity</t>
+  </si>
+  <si>
+    <t>The nuclear revolution hasn't been absorbed in military plans. Fix it</t>
+  </si>
+  <si>
+    <t>Symbols of honour, worship and ardour</t>
+  </si>
+  <si>
+    <t>WMA: Fixing a tool that has gone haywire</t>
+  </si>
+  <si>
+    <t>Fintech regulation must protect consumers, foster innovation</t>
+  </si>
+  <si>
+    <t>Eurasia holds potential</t>
+  </si>
+  <si>
+    <t>Dealing with flat productivity</t>
+  </si>
+  <si>
+    <t>India deserves UNSC seat</t>
+  </si>
+  <si>
+    <t>Fight pandemics with better animal care</t>
+  </si>
+  <si>
+    <t>India moves towards energy self-sufficiency</t>
+  </si>
+  <si>
+    <t>Time to rework Jan Vishwas Bill</t>
+  </si>
+  <si>
+    <t>Basic Structure- II</t>
+  </si>
+  <si>
+    <t>Decline of CPI</t>
+  </si>
+  <si>
+    <t>Plugging the loopholes</t>
+  </si>
+  <si>
+    <t>Empowering the youth</t>
+  </si>
+  <si>
+    <t>A sunset for royalty payments</t>
+  </si>
+  <si>
+    <t>Code red</t>
+  </si>
+  <si>
+    <t>Crime and impunity</t>
+  </si>
+  <si>
+    <t>A top-down code</t>
+  </si>
+  <si>
+    <t>Deterrence and us</t>
+  </si>
+  <si>
+    <t>Economic weather warning</t>
+  </si>
+  <si>
+    <t>Manipur's Meiteis: an erosion of identity, struggle to resurrect rich history</t>
+  </si>
+  <si>
+    <t>The slower heating of India</t>
+  </si>
+  <si>
+    <t>The law on polygamy among religious groups in India</t>
+  </si>
+  <si>
+    <t>The fallout of Putin helping make NATO 'great again'</t>
+  </si>
+  <si>
+    <t>A ground view of the Indian Space Policy 2023</t>
+  </si>
+  <si>
+    <t>Pokhran-II: A moment of profound epiphany</t>
+  </si>
+  <si>
+    <t>The troubles of India's aviation industry</t>
+  </si>
+  <si>
+    <t>India's bright continent</t>
+  </si>
+  <si>
+    <t>Balancing regulatory approaches</t>
+  </si>
+  <si>
+    <t>Wounded selves of ad hoc teachers</t>
+  </si>
+  <si>
+    <t>Though Maoism is on its last legs, the threat persists</t>
+  </si>
+  <si>
+    <t>Lots of people? Good. Tiny plots? Bad</t>
+  </si>
+  <si>
+    <t>Return of the local narrative in electoral dynamics</t>
+  </si>
+  <si>
+    <t>Reality lags rhetoric on women's representation</t>
+  </si>
+  <si>
+    <t>Keep up the spirit among those who work in India's social sector</t>
+  </si>
+  <si>
+    <t>The SVB crash could cue how to fortify banks in India</t>
+  </si>
+  <si>
+    <t>A revised Washington Consensus is beginning to attain coherence</t>
+  </si>
+  <si>
+    <t>Marriage for all, even if for a few</t>
+  </si>
+  <si>
+    <t>The problem with India's multi-alignment stand</t>
+  </si>
+  <si>
+    <t>What is the stalemate over the U.S. debt ceiling?</t>
+  </si>
+  <si>
+    <t>The SC ruling on Sena vs. Sena</t>
+  </si>
+  <si>
+    <t>The jurisdictional conflict in the running of Delhi</t>
+  </si>
+  <si>
+    <t>Rating agencies unfair to India</t>
+  </si>
+  <si>
+    <t>How RBI's new locker norms will affect you</t>
+  </si>
+  <si>
+    <t>Apprehensions over AI</t>
+  </si>
+  <si>
+    <t>Who exactly is a farmer?</t>
+  </si>
+  <si>
+    <t>SC directions to benefit electricity consumers</t>
+  </si>
+  <si>
+    <t>Anatomy of a bank failure</t>
+  </si>
+  <si>
+    <t>Colonial and ethnic rifts lie at root of Manipur clashes</t>
+  </si>
+  <si>
+    <t>Is the dollar getting dethroned? Not quite</t>
+  </si>
+  <si>
+    <t>Old is gold for consumer-facing technology companies</t>
+  </si>
+  <si>
+    <t>Bluesky has much going for it as Twitter's decentralized alter ego</t>
+  </si>
+  <si>
+    <t>The future of AI has begun to look rather too human</t>
+  </si>
+  <si>
+    <t>El Nino amid heating oceans: We're now in uncharted waters</t>
+  </si>
+  <si>
+    <t>Global investors need Indian tax carrots and not uncertainty sticks</t>
+  </si>
+  <si>
+    <t>With great power, respect</t>
+  </si>
+  <si>
+    <t>After the win</t>
+  </si>
+  <si>
+    <t>The apex court's red lines</t>
+  </si>
+  <si>
+    <t>Key takeaways from Maharashtra verdict</t>
+  </si>
+  <si>
+    <t>What tilted scales in Delhi govt's favour</t>
+  </si>
+  <si>
+    <t>The rise of Indian capital</t>
+  </si>
+  <si>
+    <t>Ancient symbiotic link between India's North, South</t>
+  </si>
+  <si>
+    <t>Ballot the only bundle of democratic joy</t>
+  </si>
+  <si>
+    <t>Give him his own money</t>
+  </si>
+  <si>
+    <t>Non-alignment fantasists</t>
+  </si>
+  <si>
+    <t>Dubious enforcers of the law</t>
+  </si>
+  <si>
+    <t>Geoeconomics and tectonic shifts in West Asia</t>
+  </si>
+  <si>
+    <t>Groundwater scene in India looks good</t>
+  </si>
+  <si>
+    <t>BP: Anti-hypertensive medication compliance is imperative</t>
   </si>
 </sst>
 </file>
@@ -52985,290 +53243,976 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5274</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5275</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5276</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5277</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5278</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5279</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5280</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5281</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5282</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5283</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5284</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5285</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5286</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>45053</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5287</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="1"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5289</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5292</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5293</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5296</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5297</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B28">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B29">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5303</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B32">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B33">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5305</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B34">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5306</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B35">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B36">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B37">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5309</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B38">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B39">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B40">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5312</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B41">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B42">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5314</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B43">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5315</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B44">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B45">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B46">
+        <v>31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B47">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5319</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B48">
+        <v>33</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B49">
+        <v>34</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5321</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B50">
+        <v>35</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5322</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B51">
+        <v>36</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5323</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B52">
+        <v>37</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5324</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B53">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5325</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B54">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>45057</v>
+      </c>
+      <c r="B55">
+        <v>40</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B59">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5331</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B61">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5333</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B62">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5334</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B63">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5336</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B66">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5338</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B67">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5339</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B68">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B69">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5341</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B70">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5342</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B71">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5343</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B72">
+        <v>17</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5344</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B73">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5345</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B74">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5346</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B75">
+        <v>20</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5347</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B76">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5348</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B77">
+        <v>22</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5349</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B78">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5350</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B79">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5351</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B80">
+        <v>25</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5352</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B81">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5353</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B82">
+        <v>27</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5354</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B83">
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5355</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B84">
+        <v>29</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5356</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B85">
+        <v>30</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B86">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5358</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>45058</v>
+      </c>
+      <c r="B87">
+        <v>32</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5359</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maadh\OneDrive\Desktop\serveup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838EEE59-42EF-4602-B9DC-DAB7C90AD36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{79DF792E-496C-4410-B1AB-E877170CAE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="405" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6385" uniqueCount="5360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6437" uniqueCount="5411">
   <si>
     <t>Unhappy nation</t>
   </si>
@@ -16139,6 +16139,159 @@
   </si>
   <si>
     <t>BP: Anti-hypertensive medication compliance is imperative</t>
+  </si>
+  <si>
+    <t>Diagnostic imaging of the Rajasthan Right to Health Act</t>
+  </si>
+  <si>
+    <t>Welfare spending has been getting a regular pruning</t>
+  </si>
+  <si>
+    <t>What's wrong with importing Russian oil?</t>
+  </si>
+  <si>
+    <t>Another opportunity for a reset in Ukraine</t>
+  </si>
+  <si>
+    <t>Bruising facelift!</t>
+  </si>
+  <si>
+    <t>No reservation please!</t>
+  </si>
+  <si>
+    <t>Yes, they can, in California</t>
+  </si>
+  <si>
+    <t>Fight of aircraft leasing firms?</t>
+  </si>
+  <si>
+    <t>Explained: Two SC verdicts</t>
+  </si>
+  <si>
+    <t>Don't let ecology fall victim to fixation with economic growth</t>
+  </si>
+  <si>
+    <t>Making RBI fit for the future</t>
+  </si>
+  <si>
+    <t>A little less lonely together</t>
+  </si>
+  <si>
+    <t>Shutting down Internet: Govts need to do rethink</t>
+  </si>
+  <si>
+    <t>One nation; many governments</t>
+  </si>
+  <si>
+    <t>G20's healing touch</t>
+  </si>
+  <si>
+    <t>Time's up for the Old Guard</t>
+  </si>
+  <si>
+    <t>Activist Patkar vs Delhi LG Saksena: recalling a case of assault from 2002</t>
+  </si>
+  <si>
+    <t>Tripura in Indo-Bangla ties</t>
+  </si>
+  <si>
+    <t>SC/ST markers: One size doesn't fit all</t>
+  </si>
+  <si>
+    <t>Ignoring the safety of women players</t>
+  </si>
+  <si>
+    <t>A break in the Western Ghats</t>
+  </si>
+  <si>
+    <t>Long Covid: a lingering problem requiring greater attention</t>
+  </si>
+  <si>
+    <t>Soil is the foundation of our planet's ecosystems</t>
+  </si>
+  <si>
+    <t>Delhi CM vs Centre: And it's not Kejriwal</t>
+  </si>
+  <si>
+    <t>A call for algorithmic justice for SC/STs</t>
+  </si>
+  <si>
+    <t>Vaccine for pancreatic cancer</t>
+  </si>
+  <si>
+    <t>Circular economy</t>
+  </si>
+  <si>
+    <t>Regulate AI for democracy</t>
+  </si>
+  <si>
+    <t>Paradox of plenty</t>
+  </si>
+  <si>
+    <t>Why India seems short of sympathy for its middle class</t>
+  </si>
+  <si>
+    <t>Emerging technologies like AI can revolutionize privacy rights</t>
+  </si>
+  <si>
+    <t>Safe banking is largely illusory so we must pursue it with care</t>
+  </si>
+  <si>
+    <t>Who moved our ghee? It has all but vanished from store shelves</t>
+  </si>
+  <si>
+    <t>Gender discrimination in farms</t>
+  </si>
+  <si>
+    <t>Information warfare and its limitations</t>
+  </si>
+  <si>
+    <t>Mitigating spillovers of financial risk</t>
+  </si>
+  <si>
+    <t>The SC verdict in the Delhi services case is a boost for democracy</t>
+  </si>
+  <si>
+    <t>It's time to tweak the nuclear policy</t>
+  </si>
+  <si>
+    <t>Med devices parks off to a slow start</t>
+  </si>
+  <si>
+    <t>Is Jagan govt aiming to turn AP into 'Alcoholic Pradesh'?</t>
+  </si>
+  <si>
+    <t>Agritech farm inputs give higher yield</t>
+  </si>
+  <si>
+    <t>SCO must be free from Chinese influence</t>
+  </si>
+  <si>
+    <t>India needs to adopt smart protein to feed its growing population</t>
+  </si>
+  <si>
+    <t>For fleeting gains</t>
+  </si>
+  <si>
+    <t>This strategic-economic bloc will only tighten the leash</t>
+  </si>
+  <si>
+    <t>The nutritional value of millets</t>
+  </si>
+  <si>
+    <t>Explainning mitochondrial donation treatment: how a baby has three parents</t>
+  </si>
+  <si>
+    <t>Low growth, low inflation ahoy</t>
+  </si>
+  <si>
+    <t>Deterrence as principle</t>
+  </si>
+  <si>
+    <t>The 'refugee scam' that trigerred a spectacle in Nepal's parliament</t>
+  </si>
+  <si>
+    <t>India's teaching troubles</t>
   </si>
 </sst>
 </file>
@@ -54189,174 +54342,590 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
+      <c r="A88" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5360</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="1"/>
+      <c r="A89" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5361</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
+      <c r="A90" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5362</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
+      <c r="A91" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B91">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5363</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
+      <c r="A92" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B92">
+        <v>5</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5364</v>
+      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
+      <c r="A93" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B93">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5365</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
+      <c r="A94" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B94">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5366</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="1"/>
+      <c r="A95" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5367</v>
+      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="1"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="1"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="1"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="1"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="1"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="1"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="1"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="1"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="1"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="1"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="1"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="1"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="1"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="1"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="1"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="1"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="1"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="1"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="1"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="1"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="1"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="1"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="1"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="1"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="1"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="1"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="1"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="1"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="1"/>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="1"/>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="1"/>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="1"/>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="1"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="1"/>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5368</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B97">
+        <v>10</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5369</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B98">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5370</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5371</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B100">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5372</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B101">
+        <v>14</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5373</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B102">
+        <v>15</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5374</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B103">
+        <v>16</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5375</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B104">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5376</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B105">
+        <v>18</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5377</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45059</v>
+      </c>
+      <c r="B106">
+        <v>19</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5378</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
+        <v>45060</v>
+      </c>
+      <c r="B107" s="8">
+        <v>1</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>5372</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5379</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5380</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B110">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5381</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B111">
+        <v>5</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5382</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B112">
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B113">
+        <v>7</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5384</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B114">
+        <v>8</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5385</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45060</v>
+      </c>
+      <c r="B115">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5386</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5388</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5389</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5390</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B120">
+        <v>5</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5391</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B121">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5392</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B122">
+        <v>7</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5393</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B123">
+        <v>8</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5394</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B124">
+        <v>9</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5395</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B125">
+        <v>10</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5396</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B126">
+        <v>11</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5397</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B127">
+        <v>12</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5398</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B128">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B130">
+        <v>15</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5401</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B131">
+        <v>16</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5402</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B132">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5403</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B133">
+        <v>18</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5404</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B134">
+        <v>19</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5405</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B135">
+        <v>20</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5406</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B136">
+        <v>21</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5407</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B137">
+        <v>22</v>
+      </c>
+      <c r="C137" t="s">
+        <v>5408</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B138">
+        <v>23</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5409</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>45061</v>
+      </c>
+      <c r="B139">
+        <v>24</v>
+      </c>
+      <c r="C139" t="s">
+        <v>5410</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
@@ -56841,6 +57410,7 @@
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A0EED197-B8C3-475A-8D35-8BDF023506E1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
